--- a/Data/Building/MeetingRoomTwo.Curtain001.xlsx
+++ b/Data/Building/MeetingRoomTwo.Curtain001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260860</v>
+        <v>1711852383</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260894</v>
+        <v>1711852972</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709272800</v>
+        <v>1711853070</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709274087</v>
+        <v>1711859478</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -610,9 +618,10 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709253367</v>
+        <v>1711931561</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709254650</v>
+        <v>1711932052</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -682,9 +692,10 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709265325</v>
+        <v>1711942012</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709266045</v>
+        <v>1711943592</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709266597</v>
+        <v>1712032875</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709267587</v>
+        <v>1712033751</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709339388</v>
+        <v>1712105463</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709340631</v>
+        <v>1712106022</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709353154</v>
+        <v>1712119381</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709354286</v>
+        <v>1712120332</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709425875</v>
+        <v>1712120495</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709427227</v>
+        <v>1712121736</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709438552</v>
+        <v>1712276004</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709441654</v>
+        <v>1712278926</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1114,7 +1136,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>physical</t>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>#4</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1162,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709513357</v>
+        <v>1712290820</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1153,6 +1180,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1199,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709514413</v>
+        <v>1712294351</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1186,9 +1214,10 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1236,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709524209</v>
+        <v>1712538178</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1254,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1273,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709528204</v>
+        <v>1712539973</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1258,9 +1288,10 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1310,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709599414</v>
+        <v>1712548380</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1328,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1347,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709600873</v>
+        <v>1712549125</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1330,9 +1362,10 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1384,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709614283</v>
+        <v>1712550686</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1402,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1421,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709615412</v>
+        <v>1712551375</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1439,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1458,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709855696</v>
+        <v>1712624626</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1476,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1495,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709856997</v>
+        <v>1712625798</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1474,9 +1510,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1532,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709944876</v>
+        <v>1712636706</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1550,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1569,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709945088</v>
+        <v>1712637537</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1546,9 +1584,10 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1606,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1710032516</v>
+        <v>1712712334</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1624,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1643,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1710032748</v>
+        <v>1712714111</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1618,9 +1658,10 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1680,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1710047079</v>
+        <v>1712722656</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1698,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1717,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1710048929</v>
+        <v>1712723939</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1735,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1754,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1710117928</v>
+        <v>1712798472</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1772,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1791,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1710126242</v>
+        <v>1712799864</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1765,6 +1809,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1828,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1710132460</v>
+        <v>1712896183</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1846,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1865,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1710133814</v>
+        <v>1712897749</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1883,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1902,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1710204333</v>
+        <v>1713140692</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1920,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1939,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1710205909</v>
+        <v>1713141529</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1906,9 +1954,10 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1976,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710219113</v>
+        <v>1713152298</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1994,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2013,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710219445</v>
+        <v>1713153704</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2031,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2050,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710463403</v>
+        <v>1713226273</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2068,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2087,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710464659</v>
+        <v>1713227304</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2050,9 +2102,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2124,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710548836</v>
+        <v>1713227323</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2142,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2161,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710549345</v>
+        <v>1713227855</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2122,9 +2176,10 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2198,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710562956</v>
+        <v>1713238167</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2216,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2235,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710564785</v>
+        <v>1713238831</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2253,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2272,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710650460</v>
+        <v>1713314475</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2233,6 +2290,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2309,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710653917</v>
+        <v>1713315194</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2266,9 +2324,10 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2346,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710722303</v>
+        <v>1713325101</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2364,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2383,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710723788</v>
+        <v>1713326902</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2401,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2420,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710734877</v>
+        <v>1713409312</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2438,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2457,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710736405</v>
+        <v>1713487940</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2475,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2494,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710808617</v>
+        <v>1713498538</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2512,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2531,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710810932</v>
+        <v>1713499884</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2482,9 +2546,10 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2568,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710822382</v>
+        <v>1713744865</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2586,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2605,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710822683</v>
+        <v>1713745884</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2623,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2642,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1711067413</v>
+        <v>1713755500</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2660,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2679,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1711068179</v>
+        <v>1713834389</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2626,9 +2694,10 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2716,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1711081543</v>
+        <v>1713918092</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2734,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2753,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1711154910</v>
+        <v>1713918716</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2771,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2790,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1711167569</v>
+        <v>1713931692</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2808,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2827,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1711168555</v>
+        <v>1713932853</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2845,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2864,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1711239538</v>
+        <v>1714002450</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2882,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2901,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1711239814</v>
+        <v>1714003513</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2842,9 +2916,10 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2938,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1711240911</v>
+        <v>1714014474</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2956,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2975,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1711241925</v>
+        <v>1714016610</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2993,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3012,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1711251605</v>
+        <v>1714101760</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2953,6 +3030,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3049,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1711254902</v>
+        <v>1714102957</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,186 +3067,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>1711338567</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>1711340740</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>1711414610</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>1711415842</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.Curtain001.state: open</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>cyber</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Curtain_Operation</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>1711426621</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>MeetingRoomTwo.Curtain001.state: close</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
